--- a/gps plan.xlsx
+++ b/gps plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/finlay/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Finlay\Documents\Projects\GPS Tractor\v1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854632A6-CD79-7E47-A017-84E0FEF022F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD861C8-D3F3-4E8B-9899-E5B8BF1087E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15920" xr2:uid="{1041D576-DF24-4D46-801B-D785A48A79C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1041D576-DF24-4D46-801B-D785A48A79C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>modes</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>need a range of power connection options, some tractors will have aux power aviaible, others will need wired onto the alternator</t>
+  </si>
+  <si>
+    <t>plow curved lines, its useful for farmer on hills etc. its called contour ploughing/ farming</t>
   </si>
 </sst>
 </file>
@@ -470,111 +473,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38FA4D12-0A6A-304E-B58F-2C10DB42274B}">
-  <dimension ref="B3:B35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B3:B38"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>20</v>
       </c>
     </row>
